--- a/Participant_Images/101/101_trials.xlsx
+++ b/Participant_Images/101/101_trials.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melanieruiz/Desktop/Rej_WTP_Choice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11A1265E-246F-DF47-A843-F7E9F3EBD66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{578593AC-74E8-AB45-9DF7-147686869C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27000" windowHeight="17440"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440"/>
   </bookViews>
   <sheets>
     <sheet name="101_trials" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'101_trials'!$A$1:$F$151</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1003,6 +1000,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="48.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
